--- a/outputs/harmonized_excels/mexico.xlsx
+++ b/outputs/harmonized_excels/mexico.xlsx
@@ -1,36 +1,133 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/06923e1dbd627e79/repos/UNGS_informalidad_comparada/outputs/harmonized_excels/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_C7FB8E5B4B9F8CE6A814FA9B56A55E91AD042B79" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{978D2D87-464E-4C37-9DC6-67FCAD764690}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2018_breakdown" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2023_breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="summary" sheetId="1" r:id="rId1"/>
+    <sheet name="2018_breakdown" sheetId="2" r:id="rId2"/>
+    <sheet name="2023_breakdown" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="27">
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>rows</t>
+  </si>
+  <si>
+    <t>total_weight</t>
+  </si>
+  <si>
+    <t>ocupado_weight</t>
+  </si>
+  <si>
+    <t>desocupado_weight</t>
+  </si>
+  <si>
+    <t>inactivo_weight</t>
+  </si>
+  <si>
+    <t>asalariado_weight</t>
+  </si>
+  <si>
+    <t>cuentapropia_weight</t>
+  </si>
+  <si>
+    <t>informal_weight</t>
+  </si>
+  <si>
+    <t>formal_weight</t>
+  </si>
+  <si>
+    <t>ocupado_pct</t>
+  </si>
+  <si>
+    <t>desocupado_pct</t>
+  </si>
+  <si>
+    <t>inactivo_pct</t>
+  </si>
+  <si>
+    <t>asalariado_pct</t>
+  </si>
+  <si>
+    <t>cuentapropia_pct</t>
+  </si>
+  <si>
+    <t>informal_pct</t>
+  </si>
+  <si>
+    <t>formal_pct</t>
+  </si>
+  <si>
+    <t>group</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>unweighted_count</t>
+  </si>
+  <si>
+    <t>ocupado</t>
+  </si>
+  <si>
+    <t>desocupado</t>
+  </si>
+  <si>
+    <t>inactivo</t>
+  </si>
+  <si>
+    <t>asalariado</t>
+  </si>
+  <si>
+    <t>cuentapropia</t>
+  </si>
+  <si>
+    <t>informal</t>
+  </si>
+  <si>
+    <t>formal</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -45,84 +142,32 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -410,205 +455,174 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="7" width="16.21875" customWidth="1"/>
+    <col min="8" max="8" width="20.77734375" customWidth="1"/>
+    <col min="9" max="15" width="16.21875" customWidth="1"/>
+    <col min="16" max="16" width="13.109375" customWidth="1"/>
+    <col min="17" max="17" width="17.109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>total_weight</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>ocupado_weight</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>desocupado_weight</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>inactivo_weight</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>asalariado_weight</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>cuentapropia_weight</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>informal_weight</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>formal_weight</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>ocupado_pct</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>desocupado_pct</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>inactivo_pct</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>asalariado_pct</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>cuentapropia_pct</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>informal_pct</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>formal_pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:17" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>2018</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="1">
         <v>1048382</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="1">
         <v>309591950</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="1">
         <v>171023371</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="1">
         <v>6365701</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="1">
         <v>132202878</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="1">
         <v>123100653</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="1">
         <v>33528350</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="1">
         <v>92357315</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="1">
         <v>217234635</v>
       </c>
-      <c r="K2" t="n">
-        <v>0.5524154326364106</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.02056158436936103</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.4270229829942284</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.3976222669872392</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.1082985200358084</v>
-      </c>
-      <c r="P2" t="n">
+      <c r="K2" s="2">
+        <v>0.55241543263641057</v>
+      </c>
+      <c r="L2" s="2">
+        <v>2.0561584369361029E-2</v>
+      </c>
+      <c r="M2" s="2">
+        <v>0.42702298299422842</v>
+      </c>
+      <c r="N2" s="2">
+        <v>0.39762226698723918</v>
+      </c>
+      <c r="O2" s="2">
+        <v>0.10829852003580839</v>
+      </c>
+      <c r="P2" s="2">
         <v>0.2983194976484369</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2" s="2">
         <v>0.7016805023515631</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>2023</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="1">
         <v>1547838</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="1">
         <v>407314538</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="1">
         <v>230472851</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="1">
         <v>6959885</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="1">
         <v>169881802</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="1">
         <v>163547378</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="1">
         <v>47730801</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="1">
         <v>121136374</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="1">
         <v>286178164</v>
       </c>
-      <c r="K3" t="n">
-        <v>0.5658350721574293</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.0170872491666379</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.4170776786759328</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.4015260020009401</v>
-      </c>
-      <c r="O3" t="n">
+      <c r="K3" s="2">
+        <v>0.56583507215742934</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1.70872491666379E-2</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0.41707767867593282</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0.40152600200094007</v>
+      </c>
+      <c r="O3" s="2">
         <v>0.1171841330151589</v>
       </c>
-      <c r="P3" t="n">
-        <v>0.29740252973735</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.70259747026265</v>
+      <c r="P3" s="2">
+        <v>0.29740252973734999</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>0.70259747026264996</v>
       </c>
     </row>
   </sheetData>
@@ -617,119 +631,99 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="13.21875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>group</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>weight</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>unweighted_count</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ocupado</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="1">
         <v>171023371</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="1">
         <v>585240</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>desocupado</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="1">
         <v>6365701</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="1">
         <v>22034</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>inactivo</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="1">
         <v>132202878</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="1">
         <v>441108</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>asalariado</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="1">
         <v>123100653</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="1">
         <v>428422</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cuentapropia</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="1">
         <v>33528350</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="1">
         <v>108035</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>informal</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="1">
         <v>92357315</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="1">
         <v>313203</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>formal</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="1">
         <v>217234635</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="1">
         <v>735179</v>
       </c>
     </row>
@@ -739,119 +733,98 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>group</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>weight</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>unweighted_count</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ocupado</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="1">
         <v>230472851</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="1">
         <v>884916</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>desocupado</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="1">
         <v>6959885</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="1">
         <v>25689</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>inactivo</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="1">
         <v>169881802</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="1">
         <v>637233</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>asalariado</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="1">
         <v>163547378</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="1">
         <v>635418</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cuentapropia</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="1">
         <v>47730801</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="1">
         <v>175573</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>informal</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="1">
         <v>121136374</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="1">
         <v>457658</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>formal</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="1">
         <v>286178164</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="1">
         <v>1090180</v>
       </c>
     </row>
